--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2375-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2375-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47E66777-331F-4A7B-B840-AECD988EBD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCFD9E2B-3349-4751-B8FC-E50786FB54A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A92E99D4-0340-423D-A63D-2D4E8FE4A7B8}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{85FD40AA-6920-4FCB-9A70-7F6D0461CD25}"/>
   </bookViews>
   <sheets>
     <sheet name="2375-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,28 +1490,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1B5067-B779-4C6F-896B-8ACC10F99883}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2959EECD-CC1E-4B46-BE11-EC3C7FE8B140}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="6.75" customWidth="1"/>
-    <col min="8" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1701,7 +1701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2023</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2022</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2021</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2019</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2018</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2017</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2016</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2015</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2014</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2013</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2012</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2011</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2010</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2009</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2008</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2007</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2006</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2005</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2004</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2003</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2002</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2001</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2000</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1999</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1998</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>1997</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1996</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>1995</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1994</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>1993</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1992</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
         <v>51</v>
       </c>
